--- a/data/trans_orig/P63-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P63-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2007</t>
+          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>71672</t>
+          <t>70514</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>88952</t>
+          <t>87528</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>66803</t>
+          <t>66314</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>90093</t>
+          <t>92319</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>144513</t>
+          <t>143147</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>173481</t>
+          <t>174715</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>68,41%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18660</t>
+          <t>20084</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35940</t>
+          <t>37098</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57688</t>
+          <t>55462</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80978</t>
+          <t>81467</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>81911</t>
+          <t>80677</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110879</t>
+          <t>112245</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,95%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>173020</t>
+          <t>173065</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>195278</t>
+          <t>195132</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>123547</t>
+          <t>125539</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>161219</t>
+          <t>161736</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>302071</t>
+          <t>305645</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>350586</t>
+          <t>353755</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>59,68%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27316</t>
+          <t>27462</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49574</t>
+          <t>49529</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>208946</t>
+          <t>208429</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>246618</t>
+          <t>244626</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>242173</t>
+          <t>239004</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>290688</t>
+          <t>287114</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>48,44%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86341</t>
+          <t>85410</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>109786</t>
+          <t>108423</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>89096</t>
+          <t>88913</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>120063</t>
+          <t>120608</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>184271</t>
+          <t>183358</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>222365</t>
+          <t>221951</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>57,8%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33357</t>
+          <t>34720</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56802</t>
+          <t>57733</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>120783</t>
+          <t>120238</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>151750</t>
+          <t>151933</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>161623</t>
+          <t>162037</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>199717</t>
+          <t>200630</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>52,25%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85212</t>
+          <t>85853</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>105609</t>
+          <t>106093</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>97498</t>
+          <t>98368</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>126943</t>
+          <t>127602</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>190875</t>
+          <t>189986</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>226426</t>
+          <t>226351</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>61,26%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28536</t>
+          <t>28052</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>48933</t>
+          <t>48292</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>108428</t>
+          <t>107769</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>137873</t>
+          <t>137003</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>143089</t>
+          <t>143164</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>178640</t>
+          <t>179529</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,59%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>62203</t>
+          <t>61914</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>77272</t>
+          <t>77594</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>73551</t>
+          <t>72796</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>98194</t>
+          <t>98030</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>142358</t>
+          <t>139633</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>171896</t>
+          <t>171091</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,37%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12106</t>
+          <t>11784</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27175</t>
+          <t>27464</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59048</t>
+          <t>59212</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>83691</t>
+          <t>84446</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>74724</t>
+          <t>75529</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>104262</t>
+          <t>106987</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>43,38%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>83377</t>
+          <t>83893</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>99921</t>
+          <t>99324</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>68687</t>
+          <t>68556</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>96685</t>
+          <t>96450</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>156689</t>
+          <t>157530</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>192200</t>
+          <t>191800</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,06%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13812</t>
+          <t>14409</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30356</t>
+          <t>29840</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>98642</t>
+          <t>98877</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>126640</t>
+          <t>126771</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>116860</t>
+          <t>117260</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>152371</t>
+          <t>151530</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,03%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>202825</t>
+          <t>204158</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>230454</t>
+          <t>229740</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>189864</t>
+          <t>189398</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>231001</t>
+          <t>233334</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>401901</t>
+          <t>403658</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>457172</t>
+          <t>456404</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,02%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>47812</t>
+          <t>48526</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>75441</t>
+          <t>74108</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>226671</t>
+          <t>224338</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>267808</t>
+          <t>268274</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>278765</t>
+          <t>279533</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>334036</t>
+          <t>332279</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,15%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>210311</t>
+          <t>210482</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>236035</t>
+          <t>234840</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>261684</t>
+          <t>258772</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>306053</t>
+          <t>307448</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>476705</t>
+          <t>477291</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>533107</t>
+          <t>536184</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>65,46%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>38510</t>
+          <t>39705</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>64234</t>
+          <t>64063</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>238478</t>
+          <t>237083</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>282847</t>
+          <t>285759</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>285970</t>
+          <t>282893</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>342372</t>
+          <t>341786</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,73%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1032624</t>
+          <t>1034857</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1092730</t>
+          <t>1096006</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1053538</t>
+          <t>1052363</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1148063</t>
+          <t>1149567</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2106175</t>
+          <t>2108241</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2228177</t>
+          <t>2224077</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>59,91%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>270685</t>
+          <t>267409</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>330791</t>
+          <t>328558</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1200871</t>
+          <t>1199367</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1295396</t>
+          <t>1296571</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1484172</t>
+          <t>1488272</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1606174</t>
+          <t>1604108</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,21%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2012</t>
+          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2012 (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>148051</t>
+          <t>148549</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>160750</t>
+          <t>161463</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>141019</t>
+          <t>139677</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>165135</t>
+          <t>165214</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>294946</t>
+          <t>293587</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>322015</t>
+          <t>321095</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,29%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7148</t>
+          <t>6435</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19847</t>
+          <t>19349</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30652</t>
+          <t>30573</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54768</t>
+          <t>56110</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41671</t>
+          <t>42591</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>68740</t>
+          <t>70099</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,27%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>270000</t>
+          <t>266943</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>295584</t>
+          <t>295256</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>146052</t>
+          <t>145136</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>186113</t>
+          <t>187611</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>420583</t>
+          <t>422428</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>477199</t>
+          <t>476322</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>65,32%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34654</t>
+          <t>34982</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>60238</t>
+          <t>63295</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>212831</t>
+          <t>211333</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>252892</t>
+          <t>253808</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>251983</t>
+          <t>252860</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>308599</t>
+          <t>306754</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>42,07%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>139737</t>
+          <t>138624</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>160113</t>
+          <t>159879</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>125027</t>
+          <t>126706</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>158336</t>
+          <t>160379</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>273569</t>
+          <t>274925</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>313703</t>
+          <t>313664</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,54%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20732</t>
+          <t>20966</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41108</t>
+          <t>42221</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>99253</t>
+          <t>97210</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>132562</t>
+          <t>130883</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>124731</t>
+          <t>124770</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>164865</t>
+          <t>163509</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,29%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>193483</t>
+          <t>194261</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>213244</t>
+          <t>213481</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>180055</t>
+          <t>180011</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>210892</t>
+          <t>210257</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>381727</t>
+          <t>381395</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>417760</t>
+          <t>418706</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,64%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17082</t>
+          <t>16845</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36843</t>
+          <t>36065</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>71625</t>
+          <t>72260</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>102462</t>
+          <t>102506</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>95083</t>
+          <t>94137</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>131116</t>
+          <t>131448</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,63%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>103918</t>
+          <t>103564</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>119141</t>
+          <t>118404</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>77112</t>
+          <t>77540</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>102814</t>
+          <t>103539</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>183975</t>
+          <t>187578</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>218236</t>
+          <t>218592</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>75,07%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9181</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24404</t>
+          <t>24758</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>60066</t>
+          <t>59341</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>85768</t>
+          <t>85340</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>72966</t>
+          <t>72610</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>107227</t>
+          <t>103624</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>35,58%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>123246</t>
+          <t>122735</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>140706</t>
+          <t>140283</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>109824</t>
+          <t>110639</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>141375</t>
+          <t>140262</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>240387</t>
+          <t>237742</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>275677</t>
+          <t>275198</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,33%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15009</t>
+          <t>15432</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32469</t>
+          <t>32980</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>83364</t>
+          <t>84477</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>114915</t>
+          <t>114100</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>104777</t>
+          <t>105256</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>140067</t>
+          <t>142712</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>37,51%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>326282</t>
+          <t>327659</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>352679</t>
+          <t>352078</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>269498</t>
+          <t>271563</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>316811</t>
+          <t>315580</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>605804</t>
+          <t>604363</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>663205</t>
+          <t>661336</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,61%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>34985</t>
+          <t>35586</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>61382</t>
+          <t>60005</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>193907</t>
+          <t>195138</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>241220</t>
+          <t>239155</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>235176</t>
+          <t>237045</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>292577</t>
+          <t>294018</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,73%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>331874</t>
+          <t>333360</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>362293</t>
+          <t>362852</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>292372</t>
+          <t>293567</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>341782</t>
+          <t>340656</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>636261</t>
+          <t>634148</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>694702</t>
+          <t>695610</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>71,18%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>52682</t>
+          <t>52123</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>83101</t>
+          <t>81615</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>220448</t>
+          <t>221574</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>269858</t>
+          <t>268663</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>282503</t>
+          <t>281595</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>340944</t>
+          <t>343057</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>35,11%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1696224</t>
+          <t>1698001</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1758590</t>
+          <t>1755582</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1433281</t>
+          <t>1434320</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1535756</t>
+          <t>1535416</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3155172</t>
+          <t>3146761</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3284902</t>
+          <t>3278176</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,4%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>237393</t>
+          <t>240401</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>299759</t>
+          <t>297982</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1059647</t>
+          <t>1059987</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1162122</t>
+          <t>1161083</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1306484</t>
+          <t>1313210</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1436214</t>
+          <t>1444625</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,46%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2016</t>
+          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2016 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>128513</t>
+          <t>127418</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>145236</t>
+          <t>145326</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>118219</t>
+          <t>119401</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>144153</t>
+          <t>144027</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>254847</t>
+          <t>254627</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>284614</t>
+          <t>285609</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,71%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12359</t>
+          <t>12269</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29082</t>
+          <t>30177</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43575</t>
+          <t>43701</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69509</t>
+          <t>68327</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>60709</t>
+          <t>59714</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>90476</t>
+          <t>90696</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,26%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>266323</t>
+          <t>267014</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>293336</t>
+          <t>294295</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>143852</t>
+          <t>143097</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>183722</t>
+          <t>186847</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>418680</t>
+          <t>417307</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>476264</t>
+          <t>472184</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>63,76%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>38943</t>
+          <t>37984</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>65956</t>
+          <t>65265</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>224599</t>
+          <t>221474</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>264469</t>
+          <t>265224</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>264336</t>
+          <t>268416</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>321920</t>
+          <t>323293</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,65%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>156550</t>
+          <t>155885</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>174811</t>
+          <t>174813</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>151354</t>
+          <t>152520</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>181714</t>
+          <t>182861</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>314692</t>
+          <t>314952</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>352576</t>
+          <t>350997</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,6%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17370</t>
+          <t>17368</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35631</t>
+          <t>36296</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67080</t>
+          <t>65933</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>97440</t>
+          <t>96274</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>88399</t>
+          <t>89978</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>126283</t>
+          <t>126023</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,58%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>202448</t>
+          <t>203451</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>226884</t>
+          <t>227633</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>176776</t>
+          <t>175692</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>210123</t>
+          <t>209204</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>388446</t>
+          <t>386412</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>430966</t>
+          <t>430680</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,47%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30900</t>
+          <t>30151</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55336</t>
+          <t>54333</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>95301</t>
+          <t>96220</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>128648</t>
+          <t>129732</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>132242</t>
+          <t>132528</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>174762</t>
+          <t>176796</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,39%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>110458</t>
+          <t>109681</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>123561</t>
+          <t>123601</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>96365</t>
+          <t>95818</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>120847</t>
+          <t>119976</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>212478</t>
+          <t>211099</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>240671</t>
+          <t>239899</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,75%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6730</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19833</t>
+          <t>20610</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42322</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>66804</t>
+          <t>67351</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>53561</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>80982</t>
+          <t>82361</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>28,07%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>117976</t>
+          <t>118922</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>136574</t>
+          <t>136885</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>67868</t>
+          <t>67278</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>95335</t>
+          <t>94006</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>192424</t>
+          <t>191492</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>230169</t>
+          <t>227886</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>64,53%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19047</t>
+          <t>18736</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>37645</t>
+          <t>36699</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>102212</t>
+          <t>103541</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>129679</t>
+          <t>130269</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>122998</t>
+          <t>125281</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>160743</t>
+          <t>161675</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,78%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>223651</t>
+          <t>223980</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>251324</t>
+          <t>250391</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>186030</t>
+          <t>184792</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>227525</t>
+          <t>227546</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>417898</t>
+          <t>417348</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>469280</t>
+          <t>470083</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>67,8%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>39858</t>
+          <t>40791</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>67531</t>
+          <t>67202</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>174624</t>
+          <t>174603</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>216119</t>
+          <t>217357</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9605,7 +9605,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>224051</t>
+          <t>223248</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>275433</t>
+          <t>275983</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,81%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>377838</t>
+          <t>375850</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>405495</t>
+          <t>404493</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>334199</t>
+          <t>333694</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>383318</t>
+          <t>382989</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>720742</t>
+          <t>718206</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>779261</t>
+          <t>777809</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,44%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>43230</t>
+          <t>44232</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>70887</t>
+          <t>72875</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>198928</t>
+          <t>199257</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>248047</t>
+          <t>248552</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>251710</t>
+          <t>253162</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>310229</t>
+          <t>312765</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,34%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1641647</t>
+          <t>1642828</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1707558</t>
+          <t>1708648</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1361163</t>
+          <t>1361597</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1460841</t>
+          <t>1461381</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3028941</t>
+          <t>3026097</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3155190</t>
+          <t>3157114</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>70,77%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>258099</t>
+          <t>257009</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>324010</t>
+          <t>322829</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1034536</t>
+          <t>1033996</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1134214</t>
+          <t>1133780</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1305844</t>
+          <t>1303920</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1432093</t>
+          <t>1434937</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,17%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2023</t>
+          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2023 (tasa de respuesta: 98,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74845</t>
+          <t>73986</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>109789</t>
+          <t>109580</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>90435</t>
+          <t>89914</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>110521</t>
+          <t>110686</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>62,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>175365</t>
+          <t>177989</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>213773</t>
+          <t>215083</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>82,16%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7453</t>
+          <t>7662</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42397</t>
+          <t>43256</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34028</t>
+          <t>33863</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54114</t>
+          <t>54635</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48018</t>
+          <t>46708</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>86426</t>
+          <t>83802</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>32,01%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>190465</t>
+          <t>194360</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>236199</t>
+          <t>236589</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>186645</t>
+          <t>186461</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>219962</t>
+          <t>220032</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>393627</t>
+          <t>394305</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>447397</t>
+          <t>446241</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>73,92%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21346</t>
+          <t>20956</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>67080</t>
+          <t>63185</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>126196</t>
+          <t>126126</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>159513</t>
+          <t>159697</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>156306</t>
+          <t>157462</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>210076</t>
+          <t>209398</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,69%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>117485</t>
+          <t>119224</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>142830</t>
+          <t>143907</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>146275</t>
+          <t>146320</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>169677</t>
+          <t>170646</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>273319</t>
+          <t>275069</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>307406</t>
+          <t>307093</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,26%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18163</t>
+          <t>17086</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43508</t>
+          <t>41769</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51969</t>
+          <t>51000</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>75371</t>
+          <t>75326</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>75233</t>
+          <t>75546</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>109320</t>
+          <t>107570</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,11%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>95457</t>
+          <t>99747</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>136915</t>
+          <t>136630</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>106536</t>
+          <t>106678</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>132111</t>
+          <t>132583</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>221137</t>
+          <t>221799</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>262221</t>
+          <t>263149</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,65%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>7101</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>48274</t>
+          <t>43984</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>81451</t>
+          <t>80979</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>107026</t>
+          <t>106884</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>95072</t>
+          <t>94144</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>136156</t>
+          <t>135494</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,92%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>42475</t>
+          <t>41946</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55866</t>
+          <t>55871</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45736</t>
+          <t>45844</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60207</t>
+          <t>58819</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>92735</t>
+          <t>92473</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>112628</t>
+          <t>112114</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>69,4%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>6328</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19724</t>
+          <t>20253</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39149</t>
+          <t>40537</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53620</t>
+          <t>53512</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>48927</t>
+          <t>49441</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>68820</t>
+          <t>69082</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,76%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>105647</t>
+          <t>103839</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>123928</t>
+          <t>123153</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>104538</t>
+          <t>104228</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>124531</t>
+          <t>124136</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>217146</t>
+          <t>215497</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>244027</t>
+          <t>243162</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,26%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7688</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25969</t>
+          <t>27777</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>43094</t>
+          <t>43489</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>63087</t>
+          <t>63397</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>55214</t>
+          <t>56079</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>82095</t>
+          <t>83744</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,99%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>204002</t>
+          <t>202297</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>248690</t>
+          <t>247712</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>353470</t>
+          <t>353107</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>498363</t>
+          <t>485731</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>592785</t>
+          <t>586549</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>736389</t>
+          <t>728581</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>90,69%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>31052</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>75740</t>
+          <t>77445</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>25264</t>
+          <t>37896</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>170157</t>
+          <t>170520</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>66980</t>
+          <t>74788</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>210584</t>
+          <t>216820</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,99%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>225497</t>
+          <t>227139</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>259468</t>
+          <t>258635</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>194490</t>
+          <t>195728</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>229993</t>
+          <t>230987</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>432616</t>
+          <t>432208</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>480432</t>
+          <t>482586</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,9%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>36526</t>
+          <t>37359</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>70497</t>
+          <t>68855</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>206296</t>
+          <t>205302</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>241799</t>
+          <t>240561</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>251851</t>
+          <t>249697</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>299667</t>
+          <t>300075</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,98%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1161421</t>
+          <t>1159417</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1250838</t>
+          <t>1249434</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1296788</t>
+          <t>1291436</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1580121</t>
+          <t>1604964</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2512451</t>
+          <t>2513521</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2789783</t>
+          <t>2788307</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,41%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>198223</t>
+          <t>199627</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>287640</t>
+          <t>289644</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>572692</t>
+          <t>547849</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>856025</t>
+          <t>861377</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>812092</t>
+          <t>813568</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1089424</t>
+          <t>1088354</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,22%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P63-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P63-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>70514</t>
+          <t>70221</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>87528</t>
+          <t>88715</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>66314</t>
+          <t>67781</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>92319</t>
+          <t>91202</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>143147</t>
+          <t>144795</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>174715</t>
+          <t>175355</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>68,66%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20084</t>
+          <t>18897</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37098</t>
+          <t>37391</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55462</t>
+          <t>56579</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>81467</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>80677</t>
+          <t>80037</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>112245</t>
+          <t>110597</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>43,3%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>173065</t>
+          <t>174493</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>195132</t>
+          <t>195711</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>125539</t>
+          <t>123844</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>161736</t>
+          <t>162049</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>305645</t>
+          <t>305169</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>353755</t>
+          <t>353111</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,57%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27462</t>
+          <t>26883</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49529</t>
+          <t>48101</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>208429</t>
+          <t>208116</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>244626</t>
+          <t>246321</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>239004</t>
+          <t>239648</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>287114</t>
+          <t>287590</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,52%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>85410</t>
+          <t>86165</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>108423</t>
+          <t>109185</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>88913</t>
+          <t>89144</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>120608</t>
+          <t>119790</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>183358</t>
+          <t>183948</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>221951</t>
+          <t>222324</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>57,9%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34720</t>
+          <t>33958</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57733</t>
+          <t>56978</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>120238</t>
+          <t>121056</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>151933</t>
+          <t>151702</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>162037</t>
+          <t>161664</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>200630</t>
+          <t>200040</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>52,1%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85853</t>
+          <t>85431</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>106093</t>
+          <t>105503</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>98368</t>
+          <t>98478</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>127602</t>
+          <t>127216</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>189986</t>
+          <t>189076</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>226351</t>
+          <t>225958</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,15%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28052</t>
+          <t>28642</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>48292</t>
+          <t>48714</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>107769</t>
+          <t>108155</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>137003</t>
+          <t>136893</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>143164</t>
+          <t>143557</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>179529</t>
+          <t>180439</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>48,83%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>61914</t>
+          <t>62671</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>77594</t>
+          <t>77430</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72796</t>
+          <t>72768</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>98030</t>
+          <t>97437</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>139633</t>
+          <t>141709</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>171091</t>
+          <t>169865</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>68,88%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11784</t>
+          <t>11948</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27464</t>
+          <t>26707</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59212</t>
+          <t>59805</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>84446</t>
+          <t>84474</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>75529</t>
+          <t>76755</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>106987</t>
+          <t>104911</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>42,54%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>83893</t>
+          <t>83284</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>99324</t>
+          <t>100332</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>68556</t>
+          <t>68587</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>96450</t>
+          <t>95400</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>157530</t>
+          <t>157524</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>191800</t>
+          <t>191631</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>62,0%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14409</t>
+          <t>13401</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29840</t>
+          <t>30449</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>98877</t>
+          <t>99927</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>126771</t>
+          <t>126740</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>117260</t>
+          <t>117429</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>151530</t>
+          <t>151536</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>204158</t>
+          <t>203688</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>229740</t>
+          <t>230566</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>189398</t>
+          <t>190643</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>233334</t>
+          <t>232369</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>403658</t>
+          <t>402730</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>456404</t>
+          <t>454937</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>61,82%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>48526</t>
+          <t>47700</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>74108</t>
+          <t>74578</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>224338</t>
+          <t>225303</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>268274</t>
+          <t>267029</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>279533</t>
+          <t>281000</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>332279</t>
+          <t>333207</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>45,28%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>210482</t>
+          <t>208507</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>234840</t>
+          <t>235309</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>258772</t>
+          <t>259944</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>307448</t>
+          <t>307142</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>477291</t>
+          <t>479683</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>536184</t>
+          <t>535944</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>65,43%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>39705</t>
+          <t>39236</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>64063</t>
+          <t>66038</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>237083</t>
+          <t>237389</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>285759</t>
+          <t>284587</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>282893</t>
+          <t>283133</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>341786</t>
+          <t>339394</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>41,44%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1034857</t>
+          <t>1037410</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1096006</t>
+          <t>1097737</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1052363</t>
+          <t>1049832</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1149567</t>
+          <t>1146176</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2108241</t>
+          <t>2105268</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2224077</t>
+          <t>2228217</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>60,02%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>267409</t>
+          <t>265678</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>328558</t>
+          <t>326005</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1199367</t>
+          <t>1202758</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1296571</t>
+          <t>1299102</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1488272</t>
+          <t>1484132</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1604108</t>
+          <t>1607081</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,29%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>148549</t>
+          <t>147782</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>161463</t>
+          <t>161280</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>139677</t>
+          <t>140601</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>165214</t>
+          <t>165854</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>293587</t>
+          <t>292613</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>321095</t>
+          <t>320986</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,26%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6435</t>
+          <t>6618</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19349</t>
+          <t>20116</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30573</t>
+          <t>29933</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56110</t>
+          <t>55186</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42591</t>
+          <t>42700</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>70099</t>
+          <t>71073</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,54%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>266943</t>
+          <t>270296</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>295256</t>
+          <t>296215</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>145136</t>
+          <t>144747</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>187611</t>
+          <t>185084</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>422428</t>
+          <t>421606</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>476322</t>
+          <t>475814</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,25%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34982</t>
+          <t>34023</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>63295</t>
+          <t>59942</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>211333</t>
+          <t>213860</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>253808</t>
+          <t>254197</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>252860</t>
+          <t>253368</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>306754</t>
+          <t>307576</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>42,18%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>138624</t>
+          <t>139110</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>159879</t>
+          <t>160710</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>126706</t>
+          <t>127872</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>160379</t>
+          <t>160623</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>274925</t>
+          <t>273284</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>313664</t>
+          <t>314091</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,64%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20966</t>
+          <t>20135</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42221</t>
+          <t>41735</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>97210</t>
+          <t>96966</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>130883</t>
+          <t>129717</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>124770</t>
+          <t>124343</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>163509</t>
+          <t>165150</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,67%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>194261</t>
+          <t>193508</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>213481</t>
+          <t>213283</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>180011</t>
+          <t>178749</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>210257</t>
+          <t>211718</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>381395</t>
+          <t>380041</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>418706</t>
+          <t>418164</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,54%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16845</t>
+          <t>17043</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36065</t>
+          <t>36818</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>72260</t>
+          <t>70799</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>102506</t>
+          <t>103768</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>94137</t>
+          <t>94679</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>131448</t>
+          <t>132802</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,9%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>103564</t>
+          <t>104132</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>118404</t>
+          <t>119097</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>77540</t>
+          <t>76248</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>103539</t>
+          <t>101941</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>187578</t>
+          <t>186157</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>218592</t>
+          <t>218142</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>74,91%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>9225</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24758</t>
+          <t>24190</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59341</t>
+          <t>60939</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>85340</t>
+          <t>86632</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>72610</t>
+          <t>73060</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>103624</t>
+          <t>105045</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>36,07%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>122735</t>
+          <t>123612</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>140283</t>
+          <t>140368</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>110639</t>
+          <t>109928</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>140262</t>
+          <t>139338</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>237742</t>
+          <t>240227</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>275198</t>
+          <t>276403</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,65%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15432</t>
+          <t>15347</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32980</t>
+          <t>32103</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>84477</t>
+          <t>85401</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>114100</t>
+          <t>114811</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>105256</t>
+          <t>104051</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>142712</t>
+          <t>140227</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>36,86%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>327659</t>
+          <t>327238</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>352078</t>
+          <t>352208</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>271563</t>
+          <t>271202</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>315580</t>
+          <t>317187</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>604363</t>
+          <t>605869</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>661336</t>
+          <t>662257</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,72%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>35586</t>
+          <t>35456</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>60005</t>
+          <t>60426</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>195138</t>
+          <t>193531</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>239155</t>
+          <t>239516</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>237045</t>
+          <t>236124</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>294018</t>
+          <t>292512</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,56%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>333360</t>
+          <t>332291</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>362852</t>
+          <t>361781</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>293567</t>
+          <t>291972</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>340656</t>
+          <t>340410</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>634148</t>
+          <t>635884</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>695610</t>
+          <t>693520</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>70,97%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>52123</t>
+          <t>53194</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>81615</t>
+          <t>82684</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>221574</t>
+          <t>221820</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>268663</t>
+          <t>270258</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>281595</t>
+          <t>283685</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>343057</t>
+          <t>341321</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>34,93%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1698001</t>
+          <t>1692782</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1755582</t>
+          <t>1755327</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1434320</t>
+          <t>1436040</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1535416</t>
+          <t>1537839</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3146761</t>
+          <t>3147525</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3278176</t>
+          <t>3275217</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,33%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>240401</t>
+          <t>240656</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>297982</t>
+          <t>303201</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1059987</t>
+          <t>1057564</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1161083</t>
+          <t>1159363</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1313210</t>
+          <t>1316169</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1444625</t>
+          <t>1443861</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,45%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>127418</t>
+          <t>126936</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>145326</t>
+          <t>145929</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>119401</t>
+          <t>119114</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>144027</t>
+          <t>144563</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>254627</t>
+          <t>255272</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>285609</t>
+          <t>285917</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,8%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>11666</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30177</t>
+          <t>30659</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43701</t>
+          <t>43165</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68327</t>
+          <t>68614</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>59714</t>
+          <t>59406</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>90696</t>
+          <t>90051</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,08%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>267014</t>
+          <t>268150</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>294295</t>
+          <t>294707</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>143097</t>
+          <t>146110</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>186847</t>
+          <t>185578</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>417307</t>
+          <t>416338</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>472184</t>
+          <t>473534</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>63,94%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37984</t>
+          <t>37572</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>65265</t>
+          <t>64129</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>221474</t>
+          <t>222743</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>265224</t>
+          <t>262211</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>268416</t>
+          <t>267066</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>323293</t>
+          <t>324262</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,78%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>155885</t>
+          <t>155550</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>174813</t>
+          <t>174527</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>152520</t>
+          <t>152126</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>182861</t>
+          <t>183471</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>314952</t>
+          <t>313696</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>350997</t>
+          <t>350271</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,43%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17368</t>
+          <t>17654</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36296</t>
+          <t>36631</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65933</t>
+          <t>65323</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>96274</t>
+          <t>96668</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>89978</t>
+          <t>90704</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>126023</t>
+          <t>127279</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,86%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>203451</t>
+          <t>204505</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>227633</t>
+          <t>227587</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>175692</t>
+          <t>175558</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>386412</t>
+          <t>388902</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>430680</t>
+          <t>430642</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,46%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30151</t>
+          <t>30197</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54333</t>
+          <t>53279</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>129732</t>
+          <t>129866</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>132528</t>
+          <t>132566</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>176796</t>
+          <t>174306</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>30,95%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>109681</t>
+          <t>110188</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>123601</t>
+          <t>123579</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>95818</t>
+          <t>96272</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>119976</t>
+          <t>120715</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>211099</t>
+          <t>211745</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>239899</t>
+          <t>240609</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,99%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>6712</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20610</t>
+          <t>20103</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>42454</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>67351</t>
+          <t>66897</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>53561</t>
+          <t>52851</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>82361</t>
+          <t>81715</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,85%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>118922</t>
+          <t>118671</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>136885</t>
+          <t>136791</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>67278</t>
+          <t>67043</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>94006</t>
+          <t>97065</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>191492</t>
+          <t>190292</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>227886</t>
+          <t>227189</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>64,33%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18736</t>
+          <t>18830</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>36699</t>
+          <t>36950</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>103541</t>
+          <t>100482</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>130269</t>
+          <t>130504</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>125281</t>
+          <t>125978</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>161675</t>
+          <t>162875</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>46,12%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>223980</t>
+          <t>223329</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>250391</t>
+          <t>250698</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>184792</t>
+          <t>186374</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>227546</t>
+          <t>227186</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>417348</t>
+          <t>415965</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>470083</t>
+          <t>470864</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>67,91%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>40791</t>
+          <t>40484</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>67202</t>
+          <t>67853</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>174603</t>
+          <t>174963</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>217357</t>
+          <t>215775</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>53,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>223248</t>
+          <t>222467</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>275983</t>
+          <t>277366</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>40,0%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>375850</t>
+          <t>375612</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>404493</t>
+          <t>403866</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>333694</t>
+          <t>333610</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>382989</t>
+          <t>383784</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>718206</t>
+          <t>720904</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>777809</t>
+          <t>780975</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,75%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>44232</t>
+          <t>44859</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>72875</t>
+          <t>73113</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>199257</t>
+          <t>198462</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>248552</t>
+          <t>248636</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>253162</t>
+          <t>249996</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>312765</t>
+          <t>310067</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,08%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1642828</t>
+          <t>1647772</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1708648</t>
+          <t>1708749</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1361597</t>
+          <t>1363543</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1461381</t>
+          <t>1461270</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3026097</t>
+          <t>3027509</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3157114</t>
+          <t>3153572</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,69%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>257009</t>
+          <t>256908</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>322829</t>
+          <t>317885</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1033996</t>
+          <t>1034107</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1133780</t>
+          <t>1131834</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1303920</t>
+          <t>1307462</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1434937</t>
+          <t>1433525</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,13%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>96245</t>
+          <t>103853</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73986</t>
+          <t>89468</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>109580</t>
+          <t>111511</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>102231</t>
+          <t>115285</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>89914</t>
+          <t>104130</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>110686</t>
+          <t>124870</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>198476</t>
+          <t>219138</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>177989</t>
+          <t>200972</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>215083</t>
+          <t>231314</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,86%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20997</t>
+          <t>12687</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7662</t>
+          <t>5029</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43256</t>
+          <t>27072</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>42318</t>
+          <t>47324</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33863</t>
+          <t>37739</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54635</t>
+          <t>58479</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>63315</t>
+          <t>60012</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46708</t>
+          <t>47836</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>83802</t>
+          <t>78178</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>28,01%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>117242</t>
+          <t>116540</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>117242</t>
+          <t>116540</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>117242</t>
+          <t>116540</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>144549</t>
+          <t>162609</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>144549</t>
+          <t>162609</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>144549</t>
+          <t>162609</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>261791</t>
+          <t>279150</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>261791</t>
+          <t>279150</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>261791</t>
+          <t>279150</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>217161</t>
+          <t>225055</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>194360</t>
+          <t>202595</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>236589</t>
+          <t>242761</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>204419</t>
+          <t>215776</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>186461</t>
+          <t>195223</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>220032</t>
+          <t>232755</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>421580</t>
+          <t>440830</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>394305</t>
+          <t>413595</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>446241</t>
+          <t>465762</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>65,31%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,88%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>40384</t>
+          <t>36572</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20956</t>
+          <t>18866</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>63185</t>
+          <t>59032</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>141739</t>
+          <t>153051</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>126126</t>
+          <t>136072</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>159697</t>
+          <t>173604</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>182123</t>
+          <t>189624</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>157462</t>
+          <t>164692</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>209398</t>
+          <t>216859</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,4%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>257545</t>
+          <t>261627</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>257545</t>
+          <t>261627</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>257545</t>
+          <t>261627</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>346158</t>
+          <t>368827</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>346158</t>
+          <t>368827</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>346158</t>
+          <t>368827</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>603703</t>
+          <t>630454</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>603703</t>
+          <t>630454</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>603703</t>
+          <t>630454</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>133071</t>
+          <t>135593</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>119224</t>
+          <t>123113</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>143907</t>
+          <t>145668</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>159366</t>
+          <t>165330</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>146320</t>
+          <t>152465</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>170646</t>
+          <t>176168</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>292438</t>
+          <t>300923</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>275069</t>
+          <t>282425</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>307093</t>
+          <t>316128</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>81,57%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>27922</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17086</t>
+          <t>14832</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41769</t>
+          <t>37387</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>62280</t>
+          <t>61738</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51000</t>
+          <t>50900</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>75326</t>
+          <t>74603</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>90201</t>
+          <t>86645</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>75546</t>
+          <t>71440</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>107570</t>
+          <t>105143</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,13%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>160993</t>
+          <t>160500</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>160993</t>
+          <t>160500</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>160993</t>
+          <t>160500</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>221646</t>
+          <t>227068</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>221646</t>
+          <t>227068</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>221646</t>
+          <t>227068</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>382639</t>
+          <t>387568</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>382639</t>
+          <t>387568</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>382639</t>
+          <t>387568</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>123912</t>
+          <t>139250</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>99747</t>
+          <t>115336</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>136630</t>
+          <t>152208</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>120376</t>
+          <t>133539</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>106678</t>
+          <t>119131</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>132583</t>
+          <t>147442</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>244288</t>
+          <t>272789</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>221799</t>
+          <t>249368</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>263149</t>
+          <t>292288</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,85%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>19819</t>
+          <t>19253</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7101</t>
+          <t>6295</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43984</t>
+          <t>43167</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>93186</t>
+          <t>103728</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>80979</t>
+          <t>89825</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>106884</t>
+          <t>118136</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>113005</t>
+          <t>122981</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>94144</t>
+          <t>103482</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>135494</t>
+          <t>146402</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>143731</t>
+          <t>158503</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>143731</t>
+          <t>158503</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>143731</t>
+          <t>158503</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>213562</t>
+          <t>237267</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>213562</t>
+          <t>237267</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>213562</t>
+          <t>237267</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>357293</t>
+          <t>395770</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>357293</t>
+          <t>395770</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>357293</t>
+          <t>395770</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>50111</t>
+          <t>53421</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41946</t>
+          <t>44690</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55871</t>
+          <t>59845</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>52558</t>
+          <t>55530</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45844</t>
+          <t>47365</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58819</t>
+          <t>63029</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>102669</t>
+          <t>108951</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>92473</t>
+          <t>97515</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>112114</t>
+          <t>119156</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>68,96%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12088</t>
+          <t>13851</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6328</t>
+          <t>7427</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20253</t>
+          <t>22582</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>46798</t>
+          <t>49978</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40537</t>
+          <t>42479</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53512</t>
+          <t>58143</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>58886</t>
+          <t>63829</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>49441</t>
+          <t>53624</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>69082</t>
+          <t>75265</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>43,56%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>62199</t>
+          <t>67272</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>62199</t>
+          <t>67272</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>62199</t>
+          <t>67272</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>99356</t>
+          <t>105508</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>99356</t>
+          <t>105508</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>99356</t>
+          <t>105508</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>161555</t>
+          <t>172780</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>161555</t>
+          <t>172780</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>161555</t>
+          <t>172780</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>115983</t>
+          <t>117978</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>103839</t>
+          <t>109687</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>123153</t>
+          <t>124414</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>114469</t>
+          <t>117481</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>104228</t>
+          <t>106036</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>124136</t>
+          <t>127717</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>230452</t>
+          <t>235459</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>215497</t>
+          <t>220967</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>243162</t>
+          <t>246947</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,12%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>15633</t>
+          <t>13203</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8463</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>27777</t>
+          <t>21494</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>53156</t>
+          <t>55742</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>43489</t>
+          <t>45506</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>63397</t>
+          <t>67187</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>68789</t>
+          <t>68946</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>56079</t>
+          <t>57458</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>83744</t>
+          <t>83438</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,41%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>131616</t>
+          <t>131181</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>131616</t>
+          <t>131181</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>131616</t>
+          <t>131181</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>167625</t>
+          <t>173223</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>167625</t>
+          <t>173223</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>167625</t>
+          <t>173223</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>299241</t>
+          <t>304405</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>299241</t>
+          <t>304405</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>299241</t>
+          <t>304405</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>228027</t>
+          <t>272441</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>202297</t>
+          <t>250333</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>247712</t>
+          <t>293487</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>424678</t>
+          <t>276471</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>353107</t>
+          <t>256280</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>485731</t>
+          <t>294809</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>652705</t>
+          <t>548912</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>586549</t>
+          <t>520148</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>728581</t>
+          <t>575379</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>81,01%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>51715</t>
+          <t>49782</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>32030</t>
+          <t>28736</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>77445</t>
+          <t>71890</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>98949</t>
+          <t>111556</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>37896</t>
+          <t>93218</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>170520</t>
+          <t>131747</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>150664</t>
+          <t>161338</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>74788</t>
+          <t>134871</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>216820</t>
+          <t>190102</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,77%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>279742</t>
+          <t>322223</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>279742</t>
+          <t>322223</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>279742</t>
+          <t>322223</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>523627</t>
+          <t>388027</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>523627</t>
+          <t>388027</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>523627</t>
+          <t>388027</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>803369</t>
+          <t>710250</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>803369</t>
+          <t>710250</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>803369</t>
+          <t>710250</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>244045</t>
+          <t>271181</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>227139</t>
+          <t>249819</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>258635</t>
+          <t>289355</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>213344</t>
+          <t>248279</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>195728</t>
+          <t>227576</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>230987</t>
+          <t>269042</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>457389</t>
+          <t>519460</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>432208</t>
+          <t>491421</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>482586</t>
+          <t>548201</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>64,68%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>51949</t>
+          <t>66971</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>37359</t>
+          <t>48797</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>68855</t>
+          <t>88333</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>222945</t>
+          <t>261163</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>205302</t>
+          <t>240400</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>240561</t>
+          <t>281866</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>274894</t>
+          <t>328134</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>249697</t>
+          <t>299393</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>300075</t>
+          <t>356173</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>42,02%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>295994</t>
+          <t>338152</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>295994</t>
+          <t>338152</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>295994</t>
+          <t>338152</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>436289</t>
+          <t>509442</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>436289</t>
+          <t>509442</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>436289</t>
+          <t>509442</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>732283</t>
+          <t>847594</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>732283</t>
+          <t>847594</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>732283</t>
+          <t>847594</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1208554</t>
+          <t>1318771</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1159417</t>
+          <t>1274910</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1249434</t>
+          <t>1359404</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1391442</t>
+          <t>1327691</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1291436</t>
+          <t>1287488</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1604964</t>
+          <t>1369894</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2599997</t>
+          <t>2646462</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2513521</t>
+          <t>2585898</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2788307</t>
+          <t>2706725</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>72,61%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>199627</t>
+          <t>196595</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>289644</t>
+          <t>281089</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>547849</t>
+          <t>802078</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>861377</t>
+          <t>884484</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>813568</t>
+          <t>1021246</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1088354</t>
+          <t>1142073</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,64%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1449061</t>
+          <t>1555999</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1449061</t>
+          <t>1555999</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1449061</t>
+          <t>1555999</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2152813</t>
+          <t>2171972</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2152813</t>
+          <t>2171972</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2152813</t>
+          <t>2171972</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>3601875</t>
+          <t>3727971</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3601875</t>
+          <t>3727971</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3601875</t>
+          <t>3727971</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
